--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="26400" windowHeight="5595"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModel" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="249">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +38,9 @@
     <t>res_name</t>
   </si>
   <si>
+    <t>unlock_id</t>
+  </si>
+  <si>
     <t>size_spine</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>资源名字</t>
   </si>
   <si>
+    <t>解锁ID</t>
+  </si>
+  <si>
     <t>spine大小缩放</t>
   </si>
   <si>
@@ -201,9 +207,6 @@
   </si>
   <si>
     <t>0.5;10,-220</t>
-  </si>
-  <si>
-    <t>测试</t>
   </si>
   <si>
     <t>Mod/Other_2/Alice_Q/Alice_2_Q_SkeletonData.asset</t>
@@ -783,13 +786,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1249,64 +1258,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
@@ -1315,10 +1324,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
@@ -1327,10 +1336,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
@@ -1339,10 +1348,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
@@ -1351,10 +1360,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
@@ -1363,10 +1372,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
@@ -1375,13 +1384,16 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1731,18 +1743,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H127"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I127"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="46.625" customWidth="1"/>
     <col min="3" max="3" width="84.125" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="7" width="62.625" customWidth="1"/>
-    <col min="8" max="8" width="42.875" customWidth="1"/>
-    <col min="9" max="9" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="29.375" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="8" width="62.625" customWidth="1"/>
+    <col min="9" max="9" width="42.875" customWidth="1"/>
+    <col min="10" max="10" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1767,308 +1781,323 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1">
+        <v>300100301</v>
+      </c>
+      <c r="E4">
         <v>1.3</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1">
+        <v>300200301</v>
+      </c>
+      <c r="E5">
         <v>1.3</v>
       </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:8">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:9">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1">
+        <v>300300301</v>
+      </c>
+      <c r="E6">
         <v>1.3</v>
       </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:8">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:9">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1">
+        <v>300400301</v>
+      </c>
+      <c r="E7">
         <v>1.3</v>
       </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:9">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
         <v>42</v>
       </c>
+      <c r="D8" s="1">
+        <v>300500301</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:9">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="D9" s="1">
+        <v>300600301</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:8">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:9">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="D10" s="1">
+        <v>300700301</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:8">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:9">
       <c r="A11">
         <v>989996</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
+        <v>57</v>
+      </c>
+      <c r="E11">
         <v>0.1</v>
       </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1" spans="1:9">
       <c r="A12">
         <v>989997</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12">
+        <v>60</v>
+      </c>
+      <c r="E12">
         <v>0.3</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1" spans="1:8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1" spans="1:9">
       <c r="A13">
         <v>989998</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13">
+        <v>63</v>
+      </c>
+      <c r="E13">
         <v>0.3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
       </c>
       <c r="G13" t="s">
         <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1" spans="1:8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1" spans="1:9">
       <c r="A14">
         <v>989999</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14">
+        <v>64</v>
+      </c>
+      <c r="E14">
         <v>0.3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
       </c>
       <c r="G14" t="s">
         <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1" spans="1:8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1" spans="1:9">
       <c r="A15">
         <v>999947</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
         <v>67</v>
       </c>
       <c r="E15" t="s">
@@ -2080,15 +2109,15 @@
       <c r="G15" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" ht="27" customHeight="1" spans="1:8">
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1" spans="1:9">
       <c r="A16">
         <v>999948</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
         <v>72</v>
       </c>
       <c r="E16" t="s">
@@ -2100,19 +2129,19 @@
       <c r="G16" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" ht="27" customHeight="1" spans="1:7">
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1" spans="1:8">
       <c r="A17">
         <v>999949</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
         <v>78</v>
@@ -2120,113 +2149,113 @@
       <c r="G17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" ht="27" customHeight="1" spans="1:7">
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1" spans="1:8">
       <c r="A18">
         <v>999950</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1" spans="1:8">
       <c r="A19">
         <v>999951</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
         <v>84</v>
       </c>
       <c r="E19" t="s">
         <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1" spans="1:8">
       <c r="A20">
         <v>999952</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1" spans="1:7">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1" spans="1:8">
       <c r="A21">
         <v>999953</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s">
         <v>90</v>
+      </c>
+      <c r="E21" t="s">
+        <v>68</v>
       </c>
       <c r="G21" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22" ht="27" customHeight="1" spans="1:7">
+      <c r="H21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1" spans="1:8">
       <c r="A22">
         <v>999954</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
         <v>93</v>
       </c>
       <c r="E22" t="s">
         <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1" spans="1:8">
       <c r="A23">
         <v>999955</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
         <v>98</v>
@@ -2234,19 +2263,19 @@
       <c r="G23" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="24" ht="27" customHeight="1" spans="1:7">
+      <c r="H23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="1:8">
       <c r="A24">
         <v>999956</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
         <v>102</v>
@@ -2254,112 +2283,112 @@
       <c r="G24" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="25" ht="27" customHeight="1" spans="1:7">
+      <c r="H24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" ht="27" customHeight="1" spans="1:8">
       <c r="A25">
         <v>999957</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" ht="27" customHeight="1" spans="1:7">
+        <v>70</v>
+      </c>
+      <c r="H25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1" spans="1:8">
       <c r="A26">
         <v>999958</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
         <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1" spans="1:8">
       <c r="A27">
         <v>999959</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" t="s">
         <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
       </c>
       <c r="G27" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="28" ht="27" customHeight="1" spans="1:7">
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1" spans="1:8">
       <c r="A28">
         <v>999960</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" ht="27" customHeight="1" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1" spans="1:8">
       <c r="A29">
         <v>999961</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" ht="27" customHeight="1" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1" spans="1:8">
       <c r="A30">
         <v>999962</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
         <v>120</v>
       </c>
       <c r="E30" t="s">
@@ -2371,39 +2400,39 @@
       <c r="G30" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" ht="27" customHeight="1" spans="1:7">
+      <c r="H30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" ht="27" customHeight="1" spans="1:8">
       <c r="A31">
         <v>999963</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" ht="27" customHeight="1" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" ht="27" customHeight="1" spans="1:8">
       <c r="A32">
         <v>999964</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
         <v>129</v>
@@ -2411,19 +2440,19 @@
       <c r="G32" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" ht="27" customHeight="1" spans="1:7">
+      <c r="H32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1" spans="1:8">
       <c r="A33">
         <v>999965</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
         <v>133</v>
@@ -2431,55 +2460,55 @@
       <c r="G33" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="34" ht="27" customHeight="1" spans="1:7">
+      <c r="H33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1" spans="1:8">
       <c r="A34">
         <v>999966</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" ht="27" customHeight="1" spans="1:8">
       <c r="A35">
         <v>999967</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" ht="27" customHeight="1" spans="1:8">
       <c r="A36">
         <v>999968</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" t="s">
         <v>141</v>
       </c>
       <c r="E36" t="s">
@@ -2491,156 +2520,156 @@
       <c r="G36" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="37" ht="27" customHeight="1" spans="1:7">
+      <c r="H36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1" spans="1:8">
       <c r="A37">
         <v>999969</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
-      </c>
-      <c r="D37" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" ht="27" customHeight="1" spans="1:8">
       <c r="A38">
         <v>999970</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="G38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" ht="27" customHeight="1" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="H38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" ht="27" customHeight="1" spans="1:8">
       <c r="A39">
         <v>999971</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1" spans="1:8">
       <c r="A40">
         <v>999972</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="G40" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" ht="27" customHeight="1" spans="1:8">
       <c r="A41">
         <v>999973</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" t="s">
         <v>157</v>
+      </c>
+      <c r="E41" t="s">
+        <v>68</v>
       </c>
       <c r="G41" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="42" ht="27" customHeight="1" spans="1:7">
+      <c r="H41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" ht="27" customHeight="1" spans="1:8">
       <c r="A42">
         <v>999974</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="G42" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43" ht="27" customHeight="1" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1" spans="1:8">
       <c r="A43">
         <v>999975</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="F43" t="s">
         <v>164</v>
       </c>
       <c r="G43" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44" ht="27" customHeight="1" spans="1:7">
+        <v>165</v>
+      </c>
+      <c r="H43" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1" spans="1:8">
       <c r="A44">
         <v>999976</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="E44" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
         <v>167</v>
@@ -2648,39 +2677,39 @@
       <c r="G44" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="45" ht="27" customHeight="1" spans="1:7">
+      <c r="H44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1" spans="1:8">
       <c r="A45">
         <v>999977</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
-      </c>
-      <c r="D45" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E45" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="F45" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="G45" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" ht="27" customHeight="1" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H45" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" ht="27" customHeight="1" spans="1:8">
       <c r="A46">
         <v>999978</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="F46" t="s">
         <v>174</v>
@@ -2688,113 +2717,113 @@
       <c r="G46" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="47" ht="27" customHeight="1" spans="1:7">
+      <c r="H46" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" ht="27" customHeight="1" spans="1:8">
       <c r="A47">
         <v>999979</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
-      </c>
-      <c r="D47" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="F47" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="48" ht="27" customHeight="1" spans="1:7">
+        <v>175</v>
+      </c>
+      <c r="H47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="48" ht="27" customHeight="1" spans="1:8">
       <c r="A48">
         <v>999980</v>
       </c>
       <c r="C48" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="F48" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="G48" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" ht="27" customHeight="1" spans="1:8">
+        <v>134</v>
+      </c>
+      <c r="H48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" ht="27" customHeight="1" spans="1:9">
       <c r="A49">
         <v>999981</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
-      </c>
-      <c r="D49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F49" t="s">
         <v>182</v>
+      </c>
+      <c r="E49" t="s">
+        <v>68</v>
       </c>
       <c r="G49" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="50" ht="27" customHeight="1" spans="1:8">
+      <c r="H49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" ht="27" customHeight="1" spans="1:9">
       <c r="A50">
         <v>999982</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
-      </c>
-      <c r="D50" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="F50" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" ht="27" customHeight="1" spans="1:8">
+        <v>165</v>
+      </c>
+      <c r="H50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1" spans="1:9">
       <c r="A51">
         <v>999983</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
-      </c>
-      <c r="D51" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51" t="s">
         <v>188</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
       </c>
       <c r="G51" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="52" ht="27" customHeight="1" spans="1:8">
+      <c r="H51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" ht="27" customHeight="1" spans="1:9">
       <c r="A52">
         <v>999984</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="F52" t="s">
         <v>192</v>
@@ -2802,36 +2831,36 @@
       <c r="G52" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="53" ht="27" customHeight="1" spans="1:8">
+      <c r="H52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="53" ht="27" customHeight="1" spans="1:9">
       <c r="A53">
         <v>999985</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
-      </c>
-      <c r="D53" t="s">
-        <v>93</v>
-      </c>
-      <c r="F53" t="s">
         <v>195</v>
+      </c>
+      <c r="E53" t="s">
+        <v>94</v>
       </c>
       <c r="G53" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="54" ht="27" customHeight="1" spans="1:8">
+      <c r="H53" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="54" ht="27" customHeight="1" spans="1:9">
       <c r="A54">
         <v>999986</v>
       </c>
       <c r="C54" t="s">
-        <v>197</v>
-      </c>
-      <c r="D54" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="E54" t="s">
-        <v>198</v>
+        <v>121</v>
       </c>
       <c r="F54" t="s">
         <v>199</v>
@@ -2839,76 +2868,76 @@
       <c r="G54" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="55" ht="27" customHeight="1" spans="1:8">
+      <c r="H54" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1" spans="1:9">
       <c r="A55">
         <v>999987</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
-      </c>
-      <c r="D55" t="s">
         <v>202</v>
       </c>
       <c r="E55" t="s">
         <v>203</v>
       </c>
       <c r="F55" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G55" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56" ht="27" customHeight="1" spans="1:8">
+        <v>200</v>
+      </c>
+      <c r="H55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1" spans="1:9">
       <c r="A56">
         <v>999988</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
-      </c>
-      <c r="D56" t="s">
-        <v>93</v>
-      </c>
-      <c r="F56" t="s">
         <v>206</v>
+      </c>
+      <c r="E56" t="s">
+        <v>94</v>
       </c>
       <c r="G56" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="57" ht="27" customHeight="1" spans="1:8">
+      <c r="H56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1" spans="1:9">
       <c r="A57">
         <v>999989</v>
       </c>
       <c r="C57" t="s">
-        <v>208</v>
-      </c>
-      <c r="D57" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="F57" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="G57" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1" spans="1:8">
+        <v>200</v>
+      </c>
+      <c r="H57" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1" spans="1:9">
       <c r="A58">
         <v>999990</v>
       </c>
       <c r="C58" t="s">
-        <v>211</v>
-      </c>
-      <c r="D58" t="s">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="E58" t="s">
-        <v>212</v>
+        <v>73</v>
       </c>
       <c r="F58" t="s">
         <v>213</v>
@@ -2919,15 +2948,15 @@
       <c r="H58" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="59" ht="27" customHeight="1" spans="1:8">
+      <c r="I58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" ht="27" customHeight="1" spans="1:9">
       <c r="A59">
         <v>999991</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
-      </c>
-      <c r="D59" t="s">
         <v>217</v>
       </c>
       <c r="E59" t="s">
@@ -2939,39 +2968,39 @@
       <c r="G59" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="60" ht="27" customHeight="1" spans="1:8">
+      <c r="H59" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="60" ht="27" customHeight="1" spans="1:9">
       <c r="A60">
         <v>999992</v>
       </c>
       <c r="C60" t="s">
-        <v>221</v>
-      </c>
-      <c r="D60" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="E60" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="F60" t="s">
         <v>223</v>
       </c>
       <c r="G60" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>224</v>
+      </c>
+      <c r="H60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61">
         <v>999993</v>
       </c>
       <c r="C61" t="s">
-        <v>224</v>
-      </c>
-      <c r="D61">
+        <v>225</v>
+      </c>
+      <c r="E61">
         <v>0.1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>225</v>
       </c>
       <c r="F61" t="s">
         <v>226</v>
@@ -2980,21 +3009,21 @@
         <v>227</v>
       </c>
       <c r="H61" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>228</v>
+      </c>
+      <c r="I61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62">
         <v>999994</v>
       </c>
       <c r="C62" t="s">
-        <v>228</v>
-      </c>
-      <c r="D62">
+        <v>229</v>
+      </c>
+      <c r="E62">
         <v>0.12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>229</v>
       </c>
       <c r="F62" t="s">
         <v>230</v>
@@ -3003,90 +3032,90 @@
         <v>231</v>
       </c>
       <c r="H62" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>232</v>
+      </c>
+      <c r="I62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>999995</v>
       </c>
       <c r="C63" t="s">
-        <v>232</v>
-      </c>
-      <c r="D63">
+        <v>233</v>
+      </c>
+      <c r="E63">
         <v>0.1</v>
       </c>
-      <c r="E63" t="s">
-        <v>233</v>
-      </c>
       <c r="F63" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="H63" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>235</v>
+      </c>
+      <c r="I63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64">
         <v>999996</v>
       </c>
       <c r="C64" t="s">
-        <v>235</v>
-      </c>
-      <c r="D64">
+        <v>236</v>
+      </c>
+      <c r="E64">
         <v>0.1</v>
       </c>
-      <c r="E64" t="s">
-        <v>236</v>
-      </c>
       <c r="F64" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="G64" t="s">
-        <v>237</v>
+        <v>123</v>
       </c>
       <c r="H64" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>238</v>
+      </c>
+      <c r="I64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65">
         <v>999997</v>
       </c>
       <c r="C65" t="s">
-        <v>238</v>
-      </c>
-      <c r="D65">
+        <v>239</v>
+      </c>
+      <c r="E65">
         <v>0.1</v>
       </c>
-      <c r="E65" t="s">
-        <v>239</v>
-      </c>
       <c r="F65" t="s">
-        <v>102</v>
+        <v>240</v>
       </c>
       <c r="G65" t="s">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="H65" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:8">
+        <v>241</v>
+      </c>
+      <c r="I65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:9">
       <c r="A66">
         <v>999998</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
-      </c>
-      <c r="D66">
+        <v>242</v>
+      </c>
+      <c r="E66">
         <v>0.1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>242</v>
       </c>
       <c r="F66" t="s">
         <v>243</v>
@@ -3095,30 +3124,33 @@
         <v>244</v>
       </c>
       <c r="H66" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>245</v>
+      </c>
+      <c r="I66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67">
         <v>999999</v>
       </c>
       <c r="C67" t="s">
-        <v>245</v>
-      </c>
-      <c r="D67">
+        <v>246</v>
+      </c>
+      <c r="E67">
         <v>0.14</v>
       </c>
-      <c r="E67" t="s">
-        <v>246</v>
-      </c>
       <c r="F67" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="G67" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="H67" t="s">
-        <v>215</v>
+        <v>248</v>
+      </c>
+      <c r="I67" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1"/>
@@ -3142,7 +3174,7 @@
     <row r="126" ht="12" customHeight="1"/>
     <row r="127" ht="12" customHeight="1"/>
   </sheetData>
-  <sortState ref="A4:U88">
+  <sortState ref="A4:V88">
     <sortCondition ref="A4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26400" windowHeight="5595"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModel" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="251">
   <si>
     <t>id</t>
   </si>
@@ -53,6 +53,9 @@
     <t>ui_data_b</t>
   </si>
   <si>
+    <t>name[language]</t>
+  </si>
+  <si>
     <t>remark</t>
   </si>
   <si>
@@ -87,6 +90,9 @@
   </si>
   <si>
     <t>ui-大卡-大小坐标</t>
+  </si>
+  <si>
+    <t>名字-中文</t>
   </si>
   <si>
     <t>备注</t>
@@ -1743,7 +1749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -1751,12 +1757,14 @@
     <col min="3" max="3" width="84.125" customWidth="1"/>
     <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="8" width="62.625" customWidth="1"/>
-    <col min="9" max="9" width="42.875" customWidth="1"/>
-    <col min="10" max="10" width="25.125" customWidth="1"/>
+    <col min="6" max="7" width="62.625" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="62.625" customWidth="1"/>
+    <col min="10" max="10" width="42.875" customWidth="1"/>
+    <col min="11" max="11" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1784,74 +1792,83 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:9">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:10">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1">
         <v>300100301</v>
@@ -1860,24 +1877,27 @@
         <v>1.3</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:9">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:10">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1">
         <v>300200301</v>
@@ -1886,24 +1906,27 @@
         <v>1.3</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:9">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>300300301</v>
@@ -1912,24 +1935,27 @@
         <v>1.3</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:9">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1">
         <v>300400301</v>
@@ -1938,1219 +1964,1402 @@
         <v>1.3</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:9">
+        <v>41</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:10">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1">
         <v>300500301</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:9">
+        <v>47</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:10">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1">
         <v>300600301</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1">
         <v>300700301</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:9">
+        <v>57</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:10">
       <c r="A11">
         <v>989996</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>0.1</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1" spans="1:9">
+        <v>61</v>
+      </c>
+      <c r="I11">
+        <v>989996</v>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1" spans="1:10">
       <c r="A12">
         <v>989997</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12">
         <v>0.3</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1" spans="1:9">
+        <v>64</v>
+      </c>
+      <c r="I12">
+        <v>989997</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1" spans="1:10">
       <c r="A13">
         <v>989998</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13">
         <v>0.3</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1" spans="1:9">
+        <v>64</v>
+      </c>
+      <c r="I13">
+        <v>989998</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1" spans="1:10">
       <c r="A14">
         <v>989999</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14">
         <v>0.3</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1" spans="1:9">
+        <v>68</v>
+      </c>
+      <c r="I14">
+        <v>989999</v>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1" spans="1:10">
       <c r="A15">
         <v>999947</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1" spans="1:9">
+        <v>73</v>
+      </c>
+      <c r="I15">
+        <v>999947</v>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1" spans="1:10">
       <c r="A16">
         <v>999948</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1" spans="1:8">
+        <v>78</v>
+      </c>
+      <c r="I16">
+        <v>999948</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1" spans="1:9">
       <c r="A17">
         <v>999949</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" ht="27" customHeight="1" spans="1:8">
+        <v>82</v>
+      </c>
+      <c r="I17">
+        <v>999949</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1" spans="1:9">
       <c r="A18">
         <v>999950</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1" spans="1:8">
+        <v>85</v>
+      </c>
+      <c r="I18">
+        <v>999950</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1" spans="1:9">
       <c r="A19">
         <v>999951</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1" spans="1:8">
+        <v>89</v>
+      </c>
+      <c r="I19">
+        <v>999951</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1" spans="1:9">
       <c r="A20">
         <v>999952</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1" spans="1:8">
+        <v>91</v>
+      </c>
+      <c r="I20">
+        <v>999952</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1" spans="1:9">
       <c r="A21">
         <v>999953</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" ht="27" customHeight="1" spans="1:8">
+        <v>94</v>
+      </c>
+      <c r="I21">
+        <v>999953</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1" spans="1:9">
       <c r="A22">
         <v>999954</v>
       </c>
       <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" t="s">
         <v>93</v>
       </c>
-      <c r="E22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" t="s">
-        <v>91</v>
-      </c>
       <c r="H22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1" spans="1:8">
+        <v>98</v>
+      </c>
+      <c r="I22">
+        <v>999954</v>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1" spans="1:9">
       <c r="A23">
         <v>999955</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" ht="27" customHeight="1" spans="1:8">
+        <v>102</v>
+      </c>
+      <c r="I23">
+        <v>999955</v>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="1:9">
       <c r="A24">
         <v>999956</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" ht="27" customHeight="1" spans="1:8">
+        <v>106</v>
+      </c>
+      <c r="I24">
+        <v>999956</v>
+      </c>
+    </row>
+    <row r="25" ht="27" customHeight="1" spans="1:9">
       <c r="A25">
         <v>999957</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" ht="27" customHeight="1" spans="1:8">
+        <v>109</v>
+      </c>
+      <c r="I25">
+        <v>999957</v>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1" spans="1:9">
       <c r="A26">
         <v>999958</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1" spans="1:8">
+        <v>113</v>
+      </c>
+      <c r="I26">
+        <v>999958</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1" spans="1:9">
       <c r="A27">
         <v>999959</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" ht="27" customHeight="1" spans="1:8">
+        <v>116</v>
+      </c>
+      <c r="I27">
+        <v>999959</v>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1" spans="1:9">
       <c r="A28">
         <v>999960</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" ht="27" customHeight="1" spans="1:8">
+        <v>119</v>
+      </c>
+      <c r="I28">
+        <v>999960</v>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1" spans="1:9">
       <c r="A29">
         <v>999961</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" ht="27" customHeight="1" spans="1:8">
+        <v>109</v>
+      </c>
+      <c r="I29">
+        <v>999961</v>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1" spans="1:9">
       <c r="A30">
         <v>999962</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" ht="27" customHeight="1" spans="1:8">
+        <v>126</v>
+      </c>
+      <c r="I30">
+        <v>999962</v>
+      </c>
+    </row>
+    <row r="31" ht="27" customHeight="1" spans="1:9">
       <c r="A31">
         <v>999963</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" ht="27" customHeight="1" spans="1:8">
+        <v>129</v>
+      </c>
+      <c r="I31">
+        <v>999963</v>
+      </c>
+    </row>
+    <row r="32" ht="27" customHeight="1" spans="1:9">
       <c r="A32">
         <v>999964</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" ht="27" customHeight="1" spans="1:8">
+        <v>133</v>
+      </c>
+      <c r="I32">
+        <v>999964</v>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1" spans="1:9">
       <c r="A33">
         <v>999965</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" ht="27" customHeight="1" spans="1:8">
+        <v>137</v>
+      </c>
+      <c r="I33">
+        <v>999965</v>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1" spans="1:9">
       <c r="A34">
         <v>999966</v>
       </c>
       <c r="C34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" t="s">
         <v>136</v>
       </c>
-      <c r="E34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" t="s">
-        <v>134</v>
-      </c>
       <c r="H34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" ht="27" customHeight="1" spans="1:8">
+        <v>133</v>
+      </c>
+      <c r="I34">
+        <v>999966</v>
+      </c>
+    </row>
+    <row r="35" ht="27" customHeight="1" spans="1:9">
       <c r="A35">
         <v>999967</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H35" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="36" ht="27" customHeight="1" spans="1:8">
+        <v>142</v>
+      </c>
+      <c r="I35">
+        <v>999967</v>
+      </c>
+    </row>
+    <row r="36" ht="27" customHeight="1" spans="1:9">
       <c r="A36">
         <v>999968</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E36" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" ht="27" customHeight="1" spans="1:8">
+        <v>147</v>
+      </c>
+      <c r="I36">
+        <v>999968</v>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1" spans="1:9">
       <c r="A37">
         <v>999969</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" ht="27" customHeight="1" spans="1:8">
+        <v>133</v>
+      </c>
+      <c r="I37">
+        <v>999969</v>
+      </c>
+    </row>
+    <row r="38" ht="27" customHeight="1" spans="1:9">
       <c r="A38">
         <v>999970</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" ht="27" customHeight="1" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="I38">
+        <v>999970</v>
+      </c>
+    </row>
+    <row r="39" ht="27" customHeight="1" spans="1:9">
       <c r="A39">
         <v>999971</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H39" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" ht="27" customHeight="1" spans="1:8">
+        <v>155</v>
+      </c>
+      <c r="I39">
+        <v>999971</v>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1" spans="1:9">
       <c r="A40">
         <v>999972</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H40" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="41" ht="27" customHeight="1" spans="1:8">
+        <v>158</v>
+      </c>
+      <c r="I40">
+        <v>999972</v>
+      </c>
+    </row>
+    <row r="41" ht="27" customHeight="1" spans="1:9">
       <c r="A41">
         <v>999973</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H41" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="42" ht="27" customHeight="1" spans="1:8">
+        <v>161</v>
+      </c>
+      <c r="I41">
+        <v>999973</v>
+      </c>
+    </row>
+    <row r="42" ht="27" customHeight="1" spans="1:9">
       <c r="A42">
         <v>999974</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H42" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" ht="27" customHeight="1" spans="1:8">
+        <v>164</v>
+      </c>
+      <c r="I42">
+        <v>999974</v>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1" spans="1:9">
       <c r="A43">
         <v>999975</v>
       </c>
       <c r="C43" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
+        <v>166</v>
+      </c>
+      <c r="G43" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" t="s">
         <v>164</v>
       </c>
-      <c r="G43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H43" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" ht="27" customHeight="1" spans="1:8">
+      <c r="I43">
+        <v>999975</v>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1" spans="1:9">
       <c r="A44">
         <v>999976</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G44" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H44" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" ht="27" customHeight="1" spans="1:8">
+        <v>171</v>
+      </c>
+      <c r="I44">
+        <v>999976</v>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1" spans="1:9">
       <c r="A45">
         <v>999977</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G45" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H45" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" ht="27" customHeight="1" spans="1:8">
+        <v>174</v>
+      </c>
+      <c r="I45">
+        <v>999977</v>
+      </c>
+    </row>
+    <row r="46" ht="27" customHeight="1" spans="1:9">
       <c r="A46">
         <v>999978</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H46" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="47" ht="27" customHeight="1" spans="1:8">
+        <v>178</v>
+      </c>
+      <c r="I46">
+        <v>999978</v>
+      </c>
+    </row>
+    <row r="47" ht="27" customHeight="1" spans="1:9">
       <c r="A47">
         <v>999979</v>
       </c>
       <c r="C47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" t="s">
+        <v>180</v>
+      </c>
+      <c r="G47" t="s">
         <v>177</v>
       </c>
-      <c r="E47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F47" t="s">
-        <v>178</v>
-      </c>
-      <c r="G47" t="s">
-        <v>175</v>
-      </c>
       <c r="H47" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="48" ht="27" customHeight="1" spans="1:8">
+        <v>181</v>
+      </c>
+      <c r="I47">
+        <v>999979</v>
+      </c>
+    </row>
+    <row r="48" ht="27" customHeight="1" spans="1:9">
       <c r="A48">
         <v>999980</v>
       </c>
       <c r="C48" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G48" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H48" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" ht="27" customHeight="1" spans="1:9">
+        <v>155</v>
+      </c>
+      <c r="I48">
+        <v>999980</v>
+      </c>
+    </row>
+    <row r="49" ht="27" customHeight="1" spans="1:10">
       <c r="A49">
         <v>999981</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H49" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="50" ht="27" customHeight="1" spans="1:9">
+        <v>186</v>
+      </c>
+      <c r="I49">
+        <v>999981</v>
+      </c>
+    </row>
+    <row r="50" ht="27" customHeight="1" spans="1:10">
       <c r="A50">
         <v>999982</v>
       </c>
       <c r="C50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H50" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="51" ht="27" customHeight="1" spans="1:9">
+        <v>189</v>
+      </c>
+      <c r="I50">
+        <v>999982</v>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1" spans="1:10">
       <c r="A51">
         <v>999983</v>
       </c>
       <c r="C51" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H51" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52" ht="27" customHeight="1" spans="1:9">
+        <v>192</v>
+      </c>
+      <c r="I51">
+        <v>999983</v>
+      </c>
+    </row>
+    <row r="52" ht="27" customHeight="1" spans="1:10">
       <c r="A52">
         <v>999984</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G52" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H52" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="53" ht="27" customHeight="1" spans="1:9">
+        <v>196</v>
+      </c>
+      <c r="I52">
+        <v>999984</v>
+      </c>
+    </row>
+    <row r="53" ht="27" customHeight="1" spans="1:10">
       <c r="A53">
         <v>999985</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G53" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H53" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="54" ht="27" customHeight="1" spans="1:9">
+        <v>199</v>
+      </c>
+      <c r="I53">
+        <v>999985</v>
+      </c>
+    </row>
+    <row r="54" ht="27" customHeight="1" spans="1:10">
       <c r="A54">
         <v>999986</v>
       </c>
       <c r="C54" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G54" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H54" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="55" ht="27" customHeight="1" spans="1:9">
+        <v>203</v>
+      </c>
+      <c r="I54">
+        <v>999986</v>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1" spans="1:10">
       <c r="A55">
         <v>999987</v>
       </c>
       <c r="C55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" t="s">
+        <v>205</v>
+      </c>
+      <c r="F55" t="s">
+        <v>206</v>
+      </c>
+      <c r="G55" t="s">
         <v>202</v>
       </c>
-      <c r="E55" t="s">
-        <v>203</v>
-      </c>
-      <c r="F55" t="s">
-        <v>204</v>
-      </c>
-      <c r="G55" t="s">
-        <v>200</v>
-      </c>
       <c r="H55" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="56" ht="27" customHeight="1" spans="1:9">
+        <v>207</v>
+      </c>
+      <c r="I55">
+        <v>999987</v>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1" spans="1:10">
       <c r="A56">
         <v>999988</v>
       </c>
       <c r="C56" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G56" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H56" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" ht="27" customHeight="1" spans="1:9">
+        <v>210</v>
+      </c>
+      <c r="I56">
+        <v>999988</v>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1" spans="1:10">
       <c r="A57">
         <v>999989</v>
       </c>
       <c r="C57" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F57" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G57" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H57" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1" spans="1:9">
+        <v>213</v>
+      </c>
+      <c r="I57">
+        <v>999989</v>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1" spans="1:10">
       <c r="A58">
         <v>999990</v>
       </c>
       <c r="C58" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G58" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H58" t="s">
-        <v>215</v>
-      </c>
-      <c r="I58" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" ht="27" customHeight="1" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="I58">
+        <v>999990</v>
+      </c>
+      <c r="J58" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" ht="27" customHeight="1" spans="1:10">
       <c r="A59">
         <v>999991</v>
       </c>
       <c r="C59" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E59" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F59" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G59" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H59" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" ht="27" customHeight="1" spans="1:9">
+        <v>223</v>
+      </c>
+      <c r="I59">
+        <v>999991</v>
+      </c>
+    </row>
+    <row r="60" ht="27" customHeight="1" spans="1:10">
       <c r="A60">
         <v>999992</v>
       </c>
       <c r="C60" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F60" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G60" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H60" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>213</v>
+      </c>
+      <c r="I60">
+        <v>999992</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>999993</v>
       </c>
       <c r="C61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E61">
         <v>0.1</v>
       </c>
       <c r="F61" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G61" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H61" t="s">
-        <v>228</v>
-      </c>
-      <c r="I61" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>230</v>
+      </c>
+      <c r="I61">
+        <v>999993</v>
+      </c>
+      <c r="J61" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>999994</v>
       </c>
       <c r="C62" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E62">
         <v>0.12</v>
       </c>
       <c r="F62" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G62" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
-      </c>
-      <c r="I62" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>234</v>
+      </c>
+      <c r="I62">
+        <v>999994</v>
+      </c>
+      <c r="J62" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>999995</v>
       </c>
       <c r="C63" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E63">
         <v>0.1</v>
       </c>
       <c r="F63" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H63" t="s">
-        <v>235</v>
-      </c>
-      <c r="I63" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>237</v>
+      </c>
+      <c r="I63">
+        <v>999995</v>
+      </c>
+      <c r="J63" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>999996</v>
       </c>
       <c r="C64" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E64">
         <v>0.1</v>
       </c>
       <c r="F64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H64" t="s">
-        <v>238</v>
-      </c>
-      <c r="I64" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+        <v>240</v>
+      </c>
+      <c r="I64">
+        <v>999996</v>
+      </c>
+      <c r="J64" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>999997</v>
       </c>
       <c r="C65" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E65">
         <v>0.1</v>
       </c>
       <c r="F65" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G65" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H65" t="s">
-        <v>241</v>
-      </c>
-      <c r="I65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:9">
+        <v>243</v>
+      </c>
+      <c r="I65">
+        <v>999997</v>
+      </c>
+      <c r="J65" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:10">
       <c r="A66">
         <v>999998</v>
       </c>
       <c r="C66" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E66">
         <v>0.1</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G66" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H66" t="s">
-        <v>245</v>
-      </c>
-      <c r="I66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+        <v>247</v>
+      </c>
+      <c r="I66">
+        <v>999998</v>
+      </c>
+      <c r="J66" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>999999</v>
       </c>
       <c r="C67" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E67">
         <v>0.14</v>
       </c>
       <c r="F67" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G67" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H67" t="s">
-        <v>248</v>
-      </c>
-      <c r="I67" t="s">
-        <v>216</v>
+        <v>250</v>
+      </c>
+      <c r="I67">
+        <v>999999</v>
+      </c>
+      <c r="J67" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1"/>
@@ -3174,7 +3383,7 @@
     <row r="126" ht="12" customHeight="1"/>
     <row r="127" ht="12" customHeight="1"/>
   </sheetData>
-  <sortState ref="A4:V88">
+  <sortState ref="A4:W88">
     <sortCondition ref="A4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModel" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <t>Human</t>
   </si>
   <si>
-    <t>Creature/Human/Human_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Human/Human_SkeletonData.asset</t>
   </si>
   <si>
     <t>2.5;0,-150</t>
@@ -116,7 +116,7 @@
     <t>Skeleton</t>
   </si>
   <si>
-    <t>Creature/Skeleton/Skeleton_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Skeleton/Skeleton_SkeletonData.asset</t>
   </si>
   <si>
     <t>2.5;-10,-150</t>
@@ -131,7 +131,7 @@
     <t>Slime</t>
   </si>
   <si>
-    <t>Creature/Slime/Slime_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Slime/Slime_SkeletonData.asset</t>
   </si>
   <si>
     <t>2.5;0,-40</t>
@@ -146,7 +146,7 @@
     <t>Succubus</t>
   </si>
   <si>
-    <t>Creature/Succubus/Succubus_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Succubus/Succubus_SkeletonData.asset</t>
   </si>
   <si>
     <t>2.5;0,-130</t>
@@ -161,7 +161,7 @@
     <t>Minotaur</t>
   </si>
   <si>
-    <t>Creature/Minotaur/Minotaur_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Minotaur/Minotaur_SkeletonData.asset</t>
   </si>
   <si>
     <t>1.3</t>
@@ -179,7 +179,7 @@
     <t>Goblin</t>
   </si>
   <si>
-    <t>Creature/Goblin/Goblin_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Goblin/Goblin_SkeletonData.asset</t>
   </si>
   <si>
     <t>3.5;-5,-110</t>
@@ -194,7 +194,7 @@
     <t>Orc</t>
   </si>
   <si>
-    <t>Creature/Orc/Orc_SkeletonData.asset</t>
+    <t>Assets/LoadResources/Spine/Creature/Orc/Orc_SkeletonData.asset</t>
   </si>
   <si>
     <t>2.5;0,-180</t>
@@ -1757,7 +1757,8 @@
     <col min="3" max="3" width="84.125" customWidth="1"/>
     <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="7" width="62.625" customWidth="1"/>
+    <col min="6" max="6" width="103" customWidth="1"/>
+    <col min="7" max="7" width="62.625" customWidth="1"/>
     <col min="8" max="8" width="17.375" customWidth="1"/>
     <col min="9" max="9" width="62.625" customWidth="1"/>
     <col min="10" max="10" width="42.875" customWidth="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModel" sheetId="1" r:id="rId1"/>
@@ -236,13 +236,13 @@
     <t>1.5;0,-200</t>
   </si>
   <si>
-    <t>Mod/Other_1/Shizhongxiaojie/Shizhongxiaojie_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Shizhongxiaojie/Shizhongxiaojie_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.13</t>
   </si>
   <si>
-    <t>Mod/Other_1/Shizhongxiaojie/Shizhongxiaojie_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Shizhongxiaojie/Shizhongxiaojie_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;0,-60</t>
@@ -251,13 +251,13 @@
     <t>0.15;-30,-50</t>
   </si>
   <si>
-    <t>Mod/Other_1/Sion/Sion_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Sion/Sion_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.11</t>
   </si>
   <si>
-    <t>Mod/Other_1/Sion/Sion_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Sion/Sion_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;0,-80</t>
@@ -266,10 +266,10 @@
     <t>0.1;0,-220</t>
   </si>
   <si>
-    <t>Mod/Other_1/Sonia/Sonia_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Sonia/Sonia_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Sonia/Sonia_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Sonia/Sonia_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;10,-80</t>
@@ -278,34 +278,34 @@
     <t>0.105;0,-220</t>
   </si>
   <si>
-    <t>Mod/Other_1/Suyite/Suyite_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Suyite/Suyite_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Suyite/Suyite_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Suyite/Suyite_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.12;0,-230</t>
   </si>
   <si>
-    <t>Mod/Other_1/Yury/Yury_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Yury/Yury_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.12</t>
   </si>
   <si>
-    <t>Mod/Other_1/Yury/Yury_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Yury/Yury_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.1;0,-200</t>
   </si>
   <si>
-    <t>Mod/Other_1/Baolilong/Baolilong_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Baolilong/Baolilong_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.6;0,-180</t>
   </si>
   <si>
-    <t>Mod/Other_1/Fusan/Fusan_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Fusan/Fusan_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;0,-55</t>
@@ -314,22 +314,22 @@
     <t>0.7;-30,-200</t>
   </si>
   <si>
-    <t>Mod/Other_1/Heishanyang/Heishanyang_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Heishanyang/Heishanyang_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.14</t>
   </si>
   <si>
-    <t>Mod/Other_1/Heishanyang/Heshanyang_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Heishanyang/Heshanyang_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.15;20,-50</t>
   </si>
   <si>
-    <t>Mod/Other_1/Molasuna/Molasuna_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Molasuna/Molasuna_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Molasuna/Molasuna_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Molasuna/Molasuna_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;5,-70</t>
@@ -338,10 +338,10 @@
     <t>0.15;0,-270</t>
   </si>
   <si>
-    <t>Mod/Other_1/Nefer/Nefer_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Nefer/Nefer_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Nefer/Nefer_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Nefer/Nefer_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;0,-70</t>
@@ -350,28 +350,28 @@
     <t>0.14;0,-330</t>
   </si>
   <si>
-    <t>Mod/Other_1/Nidiya/Nidiya_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Nidiya/Nidiya_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Nidiya/Nidiya_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Nidiya/Nidiya_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.15;0,-20</t>
   </si>
   <si>
-    <t>Mod/Other_1/Reika/Reika_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Reika/Reika_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.105</t>
   </si>
   <si>
-    <t>Mod/Other_1/Reika/Reika_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Reika/Reika_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.13;0,-320</t>
   </si>
   <si>
-    <t>Mod/Other_1/Renyu/Renyu_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Renyu/Renyu_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.3;0,-100</t>
@@ -380,28 +380,28 @@
     <t>0.6;0,-200</t>
   </si>
   <si>
-    <t>Mod/Other_1/Rose/Rosa_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Rose/Rosa_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Rose/Rosa_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Rose/Rosa_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.13;0,-300</t>
   </si>
   <si>
-    <t>Mod/Other_1/Safeierde/Safeierde_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Safeierde/Safeierde_Avator_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Saila/Saila_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Safeierde/Safeierde_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Safeierde/Safeierde_Avator_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Saila/Saila_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.1</t>
   </si>
   <si>
-    <t>Mod/Other_1/Saila/Saila_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Saila/Saila_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;0,-80</t>
@@ -410,19 +410,19 @@
     <t>0.12;0,-50</t>
   </si>
   <si>
-    <t>Mod/Other_1/Sarah/Sarah_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Sarah/Sarah_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Sarah/Sarah_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Sarah/Sarah_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.13;0,-280</t>
   </si>
   <si>
-    <t>Mod/Other_1/Lena/Lena_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Lena/Lena_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Lena/Lena_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Lena/Lena_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;0,-55</t>
@@ -431,10 +431,10 @@
     <t>0.15;0,-320</t>
   </si>
   <si>
-    <t>Mod/Other_1/Liselotte/Liselotte_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Liselotte/Liselotte_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Liselotte/Liselotte_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Liselotte/Liselotte_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;0,-67</t>
@@ -443,28 +443,28 @@
     <t>0.16;0,-360</t>
   </si>
   <si>
-    <t>Mod/Other_1/Luca/Luca_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Luca/Luca_Avator_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Luna_2/Luna_2_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Luna_2/Luna_2_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Luca/Luca_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Luca/Luca_Avator_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Luna_2/Luna_2_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Luna_2/Luna_2_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.14;10,-285</t>
   </si>
   <si>
-    <t>Mod/Other_1/Luoluo/Luoluo_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Luoluo/Luoluo_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.15</t>
   </si>
   <si>
-    <t>Mod/Other_1/Luoluo/Luoluo_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Luoluo/Luoluo_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;0,-50</t>
@@ -473,40 +473,40 @@
     <t>0.13;20,0</t>
   </si>
   <si>
-    <t>Mod/Other_1/Matoi/Matoi_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Matoi/Matoi_Avator_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Meltina/Meltina_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Meltina/Meltina_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Matoi/Matoi_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Matoi/Matoi_Avator_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Meltina/Meltina_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Meltina/Meltina_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.14;20,-310</t>
   </si>
   <si>
-    <t>Mod/Other_1/Mia/Mia_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Mia/Mia_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Mia/Mia_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Mia/Mia_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.15;20,-320</t>
   </si>
   <si>
-    <t>Mod/Other_1/Misha/Misha_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Misha/Misha_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Misha/Misha_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Misha/Misha_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.16;0,-320</t>
   </si>
   <si>
-    <t>Mod/Other_1/Guanxingzhe/Guanxingzhe_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Guanxingzhe/Guanxingzhe_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.25;0,-80</t>
@@ -515,28 +515,28 @@
     <t>0.8;20,-260</t>
   </si>
   <si>
-    <t>Mod/Other_1/Hekatiya/Hekatiya_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Hekatiya/Hekatiya_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Hekatiya/Hekatiya_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Hekatiya/Hekatiya_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;20,-350</t>
   </si>
   <si>
-    <t>Mod/Other_1/Hinagiku/Hinagiku_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Hinagiku/Hinagiku_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Hinagiku/Hinagiku_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Hinagiku/Hinagiku_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;10,-67</t>
   </si>
   <si>
-    <t>Mod/Other_1/Kuluoxier/Kuluoxier_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Kuluoxier/Kuluoxier_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Kuluoxier/Kuluoxier_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Kuluoxier/Kuluoxier_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.16;0,-67</t>
@@ -545,19 +545,19 @@
     <t>0.2;0,-20</t>
   </si>
   <si>
-    <t>Mod/Other_1/Kuluoxierback/Kuluoxierback_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Kuluoxierback/Setsuna_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Kuluoxierback/Kuluoxierback_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Kuluoxierback/Setsuna_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.5;0,-260</t>
   </si>
   <si>
-    <t>Mod/Other_1/Kutakati/Kutakati_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Kutakati/Kutakati_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Kutakati/Kutakati_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Kutakati/Kutakati_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;5,-67</t>
@@ -566,22 +566,22 @@
     <t>0.18;0,-100</t>
   </si>
   <si>
-    <t>Mod/Other_1/Leiya/Leiya_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Leiya/Leiya_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Leiya/Leiya_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Leiya/Leiya_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;20,0</t>
   </si>
   <si>
-    <t>Mod/Other_1/Luna/Luna_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Luna/Luna_Avator_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Sister/Sister_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Luna/Luna_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Luna/Luna_Avator_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Sister/Sister_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;0,-67</t>
@@ -590,16 +590,16 @@
     <t>0.7;0,-267</t>
   </si>
   <si>
-    <t>Mod/Other_1/Heitamoning/Heitamoning_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Heitamoning/Heitamoning_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Heitamoning/Heitamoning_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Heitamoning/Heitamoning_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;20,-260</t>
   </si>
   <si>
-    <t>Mod/Other_1/Mubeiling/Mubeiling_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Mubeiling/Mubeiling_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.23;0,-80</t>
@@ -608,10 +608,10 @@
     <t>0.7;0,-230</t>
   </si>
   <si>
-    <t>Mod/Other_1/Geliya/Geliya_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Geliya/Geliya_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Geliya/Geliya_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Geliya/Geliya_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;10,-80</t>
@@ -620,7 +620,7 @@
     <t>0.18;20,-80</t>
   </si>
   <si>
-    <t>Mod/Other_1/Youmingyu/Youmingyu_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Youmingyu/Youmingyu_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.25;5,-80</t>
@@ -629,10 +629,10 @@
     <t>0.8;20,-250</t>
   </si>
   <si>
-    <t>Mod/Other_1/Fulan/Fulan_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Fulan/Fulan_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Fulan/Fulan_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Fulan/Fulan_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.18;5,-90</t>
@@ -641,19 +641,19 @@
     <t>0.18;20,-200</t>
   </si>
   <si>
-    <t>Mod/Other_1/Gelinsipan/Gelinsipan_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Gelinsipan/Gelinsipan_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.09</t>
   </si>
   <si>
-    <t>Mod/Other_1/Gelinsipan/Gelinsipan_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Gelinsipan/Gelinsipan_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;20,-120</t>
   </si>
   <si>
-    <t>Mod/Other_1/Panduola/Panduola_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Panduola/Panduola_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.3;0,-110</t>
@@ -662,19 +662,19 @@
     <t>0.8;0,-250</t>
   </si>
   <si>
-    <t>Mod/Other_1/Feizhalixiu/Feizhalixiu_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Feizhalixiu/Feizhalixiu_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Feizhalixiu/Feizhalixiu_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Feizhalixiu/Feizhalixiu_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.12;0,-250</t>
   </si>
   <si>
-    <t>Mod/Other_1/Eris/Eris_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Eris/Eris_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Eris/Eris_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Eris/Eris_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;5,-80</t>
@@ -686,13 +686,13 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>Mod/Other_1/Emma/Emma_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Emma/Emma_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.115</t>
   </si>
   <si>
-    <t>Mod/Other_1/Emma/Emma_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Emma/Emma_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.22;5,-90</t>
@@ -701,19 +701,19 @@
     <t>0.115;0,-235</t>
   </si>
   <si>
-    <t>Mod/Other_1/Eleamor/Eleamor_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Eleamor/Eleamor_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Eleamor/Eleamor_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Eleamor/Eleamor_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;5,-85</t>
   </si>
   <si>
-    <t>Mod/Other_1/Bunny/Bunny_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Bunny/Bunny_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Bunny/Bunny_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Bunny/Bunny_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;5,-100</t>
@@ -722,10 +722,10 @@
     <t>0.15;0,-300</t>
   </si>
   <si>
-    <t>Mod/Other_1/Kaola/Kaola_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Kaola/Kaola_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Kaola/Kaola_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Kaola/Kaola_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.2;5,-60</t>
@@ -734,37 +734,37 @@
     <t>0.15;0,-280</t>
   </si>
   <si>
-    <t>Mod/Other_1/Bandelu/Bandelu_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Bandelu/Bandelu_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Bandelu/Bandelu_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Bandelu/Bandelu_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.16;0,-220</t>
   </si>
   <si>
-    <t>Mod/Other_1/Asitelinna/Asitelinna_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Asitelinna/Asitelinna_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Asitelinna/Asitelinna_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Asitelinna/Asitelinna_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.12;0,20</t>
   </si>
   <si>
-    <t>Mod/Other_1/Amelia/Amelia_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Amelia/Amelia_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Amelia/Amelia_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Amelia/Amelia_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.12;0,-260</t>
   </si>
   <si>
-    <t>Mod/Other_1/Aoliweiya/Aoliweiya_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Aoliweiya/Aoliweiya_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Aoliweiya/Aoliweiya_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Aoliweiya/Aoliweiya_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.16;0,-70</t>
@@ -773,10 +773,10 @@
     <t>0.15;0,-30</t>
   </si>
   <si>
-    <t>Mod/Other_1/Dunniang/Dunniang_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t>Mod/Other_1/Dunniang/Dunniang_Avator_SkeletonData.asset</t>
+    <t>Assets/ModResource/Spine/Other/Dunniang/Dunniang_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/ModResource/Spine/Other/Dunniang/Dunniang_Avator_SkeletonData.asset</t>
   </si>
   <si>
     <t>0.3;0,-230</t>
